--- a/class2/excel/exponential_model2.xlsx
+++ b/class2/excel/exponential_model2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\snguyen4\Dropbox\git\math110\class2\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sonou\Dropbox\git\math110\class2\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44D47326-F12D-4DC3-AED3-2C0BE102A372}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0564FA80-D741-45B0-BD91-AF024C885512}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17496" activeTab="1" xr2:uid="{600ADDE5-DA33-4D41-9344-51C9FFBAEA9C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17496" xr2:uid="{600ADDE5-DA33-4D41-9344-51C9FFBAEA9C}"/>
   </bookViews>
   <sheets>
     <sheet name="Example" sheetId="1" r:id="rId1"/>
@@ -189,10 +189,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1559,7 +1559,7 @@
                   </c:numRef>
                 </c:yVal>
                 <c:smooth val="0"/>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000003-A198-4D90-9D55-80A07E6FC7E0}"/>
                   </c:ext>
@@ -4682,11 +4682,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{827EFCD3-BA8E-4AC1-8498-BF5F1B96D766}" name="Table1" displayName="Table1" ref="A25:B30" totalsRowShown="0" headerRowDxfId="17" dataDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{827EFCD3-BA8E-4AC1-8498-BF5F1B96D766}" name="Table1" displayName="Table1" ref="A25:B30" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
   <autoFilter ref="A25:B30" xr:uid="{827EFCD3-BA8E-4AC1-8498-BF5F1B96D766}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{3109ED81-4EDA-4910-BBD2-987B25794220}" name="Year" dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{AE5FB2FD-C2D0-4C68-B98D-CCB080029008}" name="Population (000s)" dataDxfId="19"/>
+    <tableColumn id="1" xr3:uid="{3109ED81-4EDA-4910-BBD2-987B25794220}" name="Year" dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{AE5FB2FD-C2D0-4C68-B98D-CCB080029008}" name="Population (000s)" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
